--- a/jpcore-r4/fix/issue-924/StructureDefinition-jp-diagnosticreport-labresult.xlsx
+++ b/jpcore-r4/fix/issue-924/StructureDefinition-jp-diagnosticreport-labresult.xlsx
@@ -1074,11 +1074,11 @@
 Period</t>
   </si>
   <si>
-    <t>診断レポートの対象となる検査・処置が実施された日時</t>
+    <t>検体採取日時（effectivePeriod は未使用）</t>
   </si>
   <si>
     <t>診断手順が患者に対して実行された場合、これは実施された時刻。対象が検体である場合は、検体採取時間から診断関連時刻を導き出すことができるが、検体情報が常に入手できるとは限らず、検体と診断関連時刻の正確な関係は必ずしも自明ではない。  
-【JP Core仕様】検体採取時間</t>
+【JP Core仕様】検体採取日時</t>
   </si>
   <si>
     <t>このレポートを提出/提示するために、患者履歴のどこにあるかを知る必要があります。 / Need to know where in the patient history to file/present this report.</t>
